--- a/backend/data/ACSE Staff List.xlsx
+++ b/backend/data/ACSE Staff List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e3eece3ffa41e7d1/Desktop/ACSE_AI_Agent/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_43B16B0E76FA214D58C815D3764DB3FEBF537457" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="11_43B16B0E76FA214D58C815D3764DB3FEBF537457" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71FCF133-8088-48AD-96EC-C10703F50909}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="1000" firstSheet="24" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5328" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5415" uniqueCount="716">
   <si>
     <t>VFSTR</t>
   </si>
@@ -2233,18 +2233,31 @@
   </si>
   <si>
     <t>MRS. M. DURGA BHAVANI</t>
+  </si>
+  <si>
+    <t>Dr. J. Amar</t>
+  </si>
+  <si>
+    <t>xxxxxxxxxx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="64">
+  <fonts count="65">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3017,16 +3030,13 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="594">
+  <cellXfs count="595">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3037,461 +3047,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3500,44 +3056,339 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3545,58 +3396,220 @@
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="34" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3605,7 +3618,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3614,38 +3627,38 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3660,123 +3673,114 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="50" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3785,376 +3789,385 @@
     <xf numFmtId="0" fontId="51" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="51" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="50" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="51" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="34" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="24" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="33" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="32" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="57" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="57" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="56" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="34" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="34" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4163,235 +4176,235 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4406,85 +4419,85 @@
     <xf numFmtId="21" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="35" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="36" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4493,156 +4506,159 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -5143,6 +5159,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -5446,21 +5466,21 @@
       <c r="A1" s="526" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="523"/>
-      <c r="C1" s="523"/>
-      <c r="D1" s="523"/>
-      <c r="E1" s="523"/>
-      <c r="F1" s="523"/>
-      <c r="G1" s="523"/>
-      <c r="H1" s="523"/>
-      <c r="I1" s="523"/>
-      <c r="J1" s="523"/>
-      <c r="K1" s="523"/>
-      <c r="L1" s="523"/>
-      <c r="M1" s="523"/>
-      <c r="N1" s="523"/>
-      <c r="O1" s="523"/>
-      <c r="P1" s="523"/>
+      <c r="B1" s="520"/>
+      <c r="C1" s="520"/>
+      <c r="D1" s="520"/>
+      <c r="E1" s="520"/>
+      <c r="F1" s="520"/>
+      <c r="G1" s="520"/>
+      <c r="H1" s="520"/>
+      <c r="I1" s="520"/>
+      <c r="J1" s="520"/>
+      <c r="K1" s="520"/>
+      <c r="L1" s="520"/>
+      <c r="M1" s="520"/>
+      <c r="N1" s="520"/>
+      <c r="O1" s="520"/>
+      <c r="P1" s="520"/>
     </row>
     <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="66" t="s">
@@ -5589,11 +5609,11 @@
       </c>
       <c r="N4" s="185" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>18.09</v>
+        <v>18.10</v>
       </c>
       <c r="O4" s="218">
         <f t="shared" ca="1" si="1"/>
-        <v>18.09</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="P4" s="219">
         <v>7.05</v>
@@ -5642,11 +5662,11 @@
       </c>
       <c r="N5" s="185" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>10.09</v>
+        <v>10.10</v>
       </c>
       <c r="O5" s="218">
         <f t="shared" ca="1" si="1"/>
-        <v>10.09</v>
+        <v>10.1</v>
       </c>
       <c r="P5" s="218">
         <v>6.11</v>
@@ -5697,11 +5717,11 @@
       </c>
       <c r="N6" s="185" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
       <c r="O6" s="218">
         <f t="shared" ca="1" si="1"/>
-        <v>5.0599999999999996</v>
+        <v>5.07</v>
       </c>
       <c r="P6" s="218">
         <v>3.07</v>
@@ -5752,11 +5772,11 @@
       </c>
       <c r="N7" s="185" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>16.02</v>
+        <v>16.03</v>
       </c>
       <c r="O7" s="218">
         <f t="shared" ca="1" si="1"/>
-        <v>16.02</v>
+        <v>16.03</v>
       </c>
       <c r="P7" s="218">
         <v>2</v>
@@ -5807,11 +5827,11 @@
       </c>
       <c r="N8" s="185" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>16.08</v>
+        <v>16.09</v>
       </c>
       <c r="O8" s="218">
         <f t="shared" ca="1" si="1"/>
-        <v>16.079999999999998</v>
+        <v>16.09</v>
       </c>
       <c r="P8" s="218">
         <v>0</v>
@@ -5860,11 +5880,11 @@
       </c>
       <c r="N9" s="185" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>10.09</v>
+        <v>10.10</v>
       </c>
       <c r="O9" s="218">
         <f t="shared" ca="1" si="1"/>
-        <v>10.09</v>
+        <v>10.1</v>
       </c>
       <c r="P9" s="218">
         <v>0</v>
@@ -5913,11 +5933,11 @@
       </c>
       <c r="N10" s="185" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>10.04</v>
+        <v>10.05</v>
       </c>
       <c r="O10" s="218">
         <f t="shared" ca="1" si="1"/>
-        <v>10.039999999999999</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="P10" s="218">
         <v>2.0699999999999998</v>
@@ -6042,11 +6062,11 @@
       </c>
       <c r="N13" s="185" t="str">
         <f ca="1">DATEDIF(M13,TODAY(),"Y")&amp;"."&amp;TEXT(DATEDIF(M13,TODAY(),"YM"),"00")</f>
-        <v>3.00</v>
+        <v>3.01</v>
       </c>
       <c r="O13" s="218">
         <f ca="1">LEFT(N13,FIND(".",N13)-1)+IF(LEN(RIGHT(N13,LEN(N13)-FIND(".",N13)))=1,CONCATENATE("0.0",RIGHT(N13,LEN(N13)-FIND(".",N13))),CONCATENATE("0.",RIGHT(N13,LEN(N13)-FIND(".",N13))))</f>
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="P13" s="218">
         <v>1.03</v>
@@ -8105,13 +8125,13 @@
       <c r="E2" s="516"/>
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="522" t="s">
+      <c r="A3" s="519" t="s">
         <v>444</v>
       </c>
-      <c r="B3" s="523"/>
-      <c r="C3" s="523"/>
-      <c r="D3" s="523"/>
-      <c r="E3" s="523"/>
+      <c r="B3" s="520"/>
+      <c r="C3" s="520"/>
+      <c r="D3" s="520"/>
+      <c r="E3" s="520"/>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="553" t="s">
@@ -9154,10 +9174,10 @@
       <c r="A69" s="542" t="s">
         <v>411</v>
       </c>
-      <c r="B69" s="523"/>
-      <c r="C69" s="523"/>
-      <c r="D69" s="523"/>
-      <c r="E69" s="523"/>
+      <c r="B69" s="520"/>
+      <c r="C69" s="520"/>
+      <c r="D69" s="520"/>
+      <c r="E69" s="520"/>
     </row>
     <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A70" s="53">
@@ -9351,13 +9371,13 @@
       <c r="E2" s="516"/>
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="522" t="s">
+      <c r="A3" s="519" t="s">
         <v>444</v>
       </c>
-      <c r="B3" s="523"/>
-      <c r="C3" s="523"/>
-      <c r="D3" s="523"/>
-      <c r="E3" s="523"/>
+      <c r="B3" s="520"/>
+      <c r="C3" s="520"/>
+      <c r="D3" s="520"/>
+      <c r="E3" s="520"/>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="553" t="s">
@@ -10499,10 +10519,10 @@
       <c r="A76" s="542" t="s">
         <v>411</v>
       </c>
-      <c r="B76" s="523"/>
-      <c r="C76" s="523"/>
-      <c r="D76" s="523"/>
-      <c r="E76" s="523"/>
+      <c r="B76" s="520"/>
+      <c r="C76" s="520"/>
+      <c r="D76" s="520"/>
+      <c r="E76" s="520"/>
     </row>
     <row r="77" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A77" s="53">
@@ -10721,15 +10741,15 @@
       <c r="G3" s="555"/>
     </row>
     <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="522" t="s">
+      <c r="A4" s="519" t="s">
         <v>447</v>
       </c>
-      <c r="B4" s="523"/>
-      <c r="C4" s="523"/>
-      <c r="D4" s="523"/>
-      <c r="E4" s="523"/>
-      <c r="F4" s="523"/>
-      <c r="G4" s="523"/>
+      <c r="B4" s="520"/>
+      <c r="C4" s="520"/>
+      <c r="D4" s="520"/>
+      <c r="E4" s="520"/>
+      <c r="F4" s="520"/>
+      <c r="G4" s="520"/>
     </row>
     <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="553" t="s">
@@ -11876,14 +11896,14 @@
       <c r="F2" s="516"/>
     </row>
     <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="522" t="s">
+      <c r="A3" s="519" t="s">
         <v>469</v>
       </c>
-      <c r="B3" s="523"/>
-      <c r="C3" s="523"/>
-      <c r="D3" s="523"/>
-      <c r="E3" s="523"/>
-      <c r="F3" s="523"/>
+      <c r="B3" s="520"/>
+      <c r="C3" s="520"/>
+      <c r="D3" s="520"/>
+      <c r="E3" s="520"/>
+      <c r="F3" s="520"/>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="553" t="s">
@@ -12747,11 +12767,11 @@
     </row>
     <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A53" s="557"/>
-      <c r="B53" s="523"/>
-      <c r="C53" s="523"/>
-      <c r="D53" s="523"/>
-      <c r="E53" s="523"/>
-      <c r="F53" s="535"/>
+      <c r="B53" s="520"/>
+      <c r="C53" s="520"/>
+      <c r="D53" s="520"/>
+      <c r="E53" s="520"/>
+      <c r="F53" s="537"/>
     </row>
     <row r="54" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A54" s="53">
@@ -13022,10 +13042,10 @@
       <c r="A73" s="542" t="s">
         <v>411</v>
       </c>
-      <c r="B73" s="523"/>
-      <c r="C73" s="523"/>
-      <c r="D73" s="523"/>
-      <c r="E73" s="523"/>
+      <c r="B73" s="520"/>
+      <c r="C73" s="520"/>
+      <c r="D73" s="520"/>
+      <c r="E73" s="520"/>
     </row>
     <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A74" s="53">
@@ -13689,7 +13709,7 @@
       </c>
       <c r="H22" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="17.25" customHeight="1">
@@ -14386,7 +14406,7 @@
       </c>
       <c r="H52" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="17.25" customHeight="1">
@@ -15357,7 +15377,7 @@
       </c>
       <c r="G21" s="123">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -16053,7 +16073,7 @@
       </c>
       <c r="G50" s="123">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -16416,10 +16436,10 @@
       <c r="A71" s="542" t="s">
         <v>411</v>
       </c>
-      <c r="B71" s="523"/>
-      <c r="C71" s="523"/>
-      <c r="D71" s="523"/>
-      <c r="E71" s="523"/>
+      <c r="B71" s="520"/>
+      <c r="C71" s="520"/>
+      <c r="D71" s="520"/>
+      <c r="E71" s="520"/>
       <c r="F71" s="52"/>
     </row>
     <row r="72" spans="1:6" ht="20.100000000000001" customHeight="1">
@@ -17137,7 +17157,7 @@
       </c>
       <c r="H21" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="20.100000000000001" customHeight="1">
@@ -17871,7 +17891,7 @@
       </c>
       <c r="H52" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="20.100000000000001" customHeight="1">
@@ -18214,10 +18234,10 @@
       <c r="B72" s="542" t="s">
         <v>411</v>
       </c>
-      <c r="C72" s="523"/>
-      <c r="D72" s="523"/>
-      <c r="E72" s="523"/>
-      <c r="F72" s="523"/>
+      <c r="C72" s="520"/>
+      <c r="D72" s="520"/>
+      <c r="E72" s="520"/>
+      <c r="F72" s="520"/>
       <c r="G72" s="52"/>
     </row>
     <row r="73" spans="2:7" ht="20.100000000000001" customHeight="1">
@@ -18481,7 +18501,7 @@
       <c r="F2" s="516"/>
     </row>
     <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="521" t="s">
+      <c r="A3" s="518" t="s">
         <v>488</v>
       </c>
       <c r="B3" s="516"/>
@@ -18893,7 +18913,7 @@
       </c>
       <c r="G20">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -19649,7 +19669,7 @@
       </c>
       <c r="G51">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="20.100000000000001" customHeight="1">
@@ -20320,10 +20340,10 @@
       <c r="A88" s="542" t="s">
         <v>411</v>
       </c>
-      <c r="B88" s="523"/>
-      <c r="C88" s="523"/>
-      <c r="D88" s="523"/>
-      <c r="E88" s="523"/>
+      <c r="B88" s="520"/>
+      <c r="C88" s="520"/>
+      <c r="D88" s="520"/>
+      <c r="E88" s="520"/>
       <c r="F88" s="254"/>
     </row>
     <row r="89" spans="1:6" ht="20.100000000000001" customHeight="1">
@@ -20884,7 +20904,7 @@
       <c r="G2" s="516"/>
     </row>
     <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="521" t="s">
+      <c r="A3" s="518" t="s">
         <v>488</v>
       </c>
       <c r="B3" s="515"/>
@@ -21307,7 +21327,7 @@
       </c>
       <c r="G21" s="123">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -22016,7 +22036,7 @@
       </c>
       <c r="G51" s="123">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="20.100000000000001" customHeight="1">
@@ -23469,10 +23489,10 @@
     </row>
     <row r="125" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A125" s="542"/>
-      <c r="B125" s="523"/>
-      <c r="C125" s="523"/>
-      <c r="D125" s="523"/>
-      <c r="E125" s="523"/>
+      <c r="B125" s="520"/>
+      <c r="C125" s="520"/>
+      <c r="D125" s="520"/>
+      <c r="E125" s="520"/>
       <c r="F125" s="254"/>
     </row>
     <row r="126" spans="1:6" ht="20.100000000000001" customHeight="1">
@@ -24000,7 +24020,7 @@
       <c r="I2" s="515"/>
     </row>
     <row r="3" spans="2:9" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="521" t="s">
+      <c r="B3" s="518" t="s">
         <v>488</v>
       </c>
       <c r="C3" s="533"/>
@@ -24440,7 +24460,7 @@
       </c>
       <c r="H21" s="89">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="123"/>
     </row>
@@ -25110,7 +25130,7 @@
       </c>
       <c r="H48" s="89">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="123"/>
     </row>
@@ -26645,10 +26665,10 @@
     </row>
     <row r="130" spans="2:7" ht="20.100000000000001" customHeight="1">
       <c r="B130" s="542"/>
-      <c r="C130" s="523"/>
-      <c r="D130" s="523"/>
-      <c r="E130" s="523"/>
-      <c r="F130" s="523"/>
+      <c r="C130" s="520"/>
+      <c r="D130" s="520"/>
+      <c r="E130" s="520"/>
+      <c r="F130" s="520"/>
       <c r="G130" s="254"/>
     </row>
     <row r="131" spans="2:7" ht="20.100000000000001" customHeight="1">
@@ -26862,11 +26882,11 @@
       <c r="B2" s="526" t="s">
         <v>324</v>
       </c>
-      <c r="C2" s="523"/>
-      <c r="D2" s="523"/>
-      <c r="E2" s="523"/>
-      <c r="F2" s="523"/>
-      <c r="G2" s="523"/>
+      <c r="C2" s="520"/>
+      <c r="D2" s="520"/>
+      <c r="E2" s="520"/>
+      <c r="F2" s="520"/>
+      <c r="G2" s="520"/>
     </row>
     <row r="3" spans="2:7" ht="20.100000000000001" customHeight="1">
       <c r="B3" s="527" t="s">
@@ -27855,7 +27875,7 @@
       <c r="I2" s="515"/>
     </row>
     <row r="3" spans="2:9" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="521" t="s">
+      <c r="B3" s="518" t="s">
         <v>488</v>
       </c>
       <c r="C3" s="533"/>
@@ -28295,7 +28315,7 @@
       </c>
       <c r="H21" s="89">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="123"/>
     </row>
@@ -28983,7 +29003,7 @@
       </c>
       <c r="H49" s="89">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="123"/>
     </row>
@@ -30507,10 +30527,10 @@
     </row>
     <row r="127" spans="2:7" ht="20.100000000000001" customHeight="1">
       <c r="B127" s="542"/>
-      <c r="C127" s="523"/>
-      <c r="D127" s="523"/>
-      <c r="E127" s="523"/>
-      <c r="F127" s="523"/>
+      <c r="C127" s="520"/>
+      <c r="D127" s="520"/>
+      <c r="E127" s="520"/>
+      <c r="F127" s="520"/>
       <c r="G127" s="254"/>
     </row>
     <row r="128" spans="2:7" ht="20.100000000000001" customHeight="1">
@@ -30730,7 +30750,7 @@
       <c r="G2" s="516"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1">
-      <c r="A3" s="521" t="s">
+      <c r="A3" s="518" t="s">
         <v>488</v>
       </c>
       <c r="B3" s="578"/>
@@ -31143,7 +31163,7 @@
       </c>
       <c r="G21" s="89">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1">
@@ -31824,7 +31844,7 @@
       </c>
       <c r="G50" s="89">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="14.4" customHeight="1">
@@ -31941,12 +31961,12 @@
       <c r="A57" s="579" t="s">
         <v>576</v>
       </c>
-      <c r="B57" s="523"/>
-      <c r="C57" s="523"/>
-      <c r="D57" s="523"/>
-      <c r="E57" s="523"/>
-      <c r="F57" s="523"/>
-      <c r="G57" s="535"/>
+      <c r="B57" s="520"/>
+      <c r="C57" s="520"/>
+      <c r="D57" s="520"/>
+      <c r="E57" s="520"/>
+      <c r="F57" s="520"/>
+      <c r="G57" s="537"/>
       <c r="J57" s="435" t="s">
         <v>577</v>
       </c>
@@ -33181,10 +33201,10 @@
     </row>
     <row r="120" spans="1:6" ht="15.6" customHeight="1">
       <c r="A120" s="542"/>
-      <c r="B120" s="523"/>
-      <c r="C120" s="523"/>
-      <c r="D120" s="523"/>
-      <c r="E120" s="523"/>
+      <c r="B120" s="520"/>
+      <c r="C120" s="520"/>
+      <c r="D120" s="520"/>
+      <c r="E120" s="520"/>
       <c r="F120" s="254"/>
     </row>
     <row r="121" spans="1:6">
@@ -33279,15 +33299,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A57:G57"/>
     <mergeCell ref="A58:E58"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A120:E120"/>
-    <mergeCell ref="A55:E55"/>
   </mergeCells>
   <conditionalFormatting sqref="B20:B21">
     <cfRule type="duplicateValues" dxfId="9" priority="1"/>
@@ -33756,7 +33776,7 @@
       </c>
       <c r="G21" s="426">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" s="432"/>
     </row>
@@ -34394,7 +34414,7 @@
       </c>
       <c r="G48" s="426">
         <f ca="1">DATEDIF(F48,TODAY(),"y")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="395" customFormat="1" ht="16.5" customHeight="1">
@@ -34531,11 +34551,11 @@
       <c r="A56" s="583" t="s">
         <v>1</v>
       </c>
-      <c r="B56" s="523"/>
-      <c r="C56" s="523"/>
-      <c r="D56" s="523"/>
-      <c r="E56" s="523"/>
-      <c r="F56" s="523"/>
+      <c r="B56" s="520"/>
+      <c r="C56" s="520"/>
+      <c r="D56" s="520"/>
+      <c r="E56" s="520"/>
+      <c r="F56" s="520"/>
     </row>
     <row r="57" spans="1:7" ht="18" customHeight="1">
       <c r="A57" s="565" t="s">
@@ -35409,11 +35429,11 @@
       <c r="A100" s="584" t="s">
         <v>114</v>
       </c>
-      <c r="B100" s="523"/>
-      <c r="C100" s="523"/>
-      <c r="D100" s="523"/>
-      <c r="E100" s="523"/>
-      <c r="F100" s="523"/>
+      <c r="B100" s="520"/>
+      <c r="C100" s="520"/>
+      <c r="D100" s="520"/>
+      <c r="E100" s="520"/>
+      <c r="F100" s="520"/>
     </row>
     <row r="101" spans="1:7" s="395" customFormat="1" ht="18" customHeight="1">
       <c r="A101" s="306">
@@ -35903,7 +35923,7 @@
       <c r="I2" s="587"/>
     </row>
     <row r="3" spans="1:9" ht="18" customHeight="1">
-      <c r="A3" s="521" t="s">
+      <c r="A3" s="518" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="539"/>
@@ -35917,14 +35937,14 @@
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1">
       <c r="A4" s="589"/>
-      <c r="B4" s="523"/>
-      <c r="C4" s="523"/>
-      <c r="D4" s="523"/>
-      <c r="E4" s="523"/>
-      <c r="F4" s="523"/>
-      <c r="G4" s="523"/>
-      <c r="H4" s="523"/>
-      <c r="I4" s="523"/>
+      <c r="B4" s="520"/>
+      <c r="C4" s="520"/>
+      <c r="D4" s="520"/>
+      <c r="E4" s="520"/>
+      <c r="F4" s="520"/>
+      <c r="G4" s="520"/>
+      <c r="H4" s="520"/>
+      <c r="I4" s="520"/>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -36418,7 +36438,7 @@
       </c>
       <c r="G21" s="469">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="468" t="s">
         <v>207</v>
@@ -37163,7 +37183,7 @@
       </c>
       <c r="G47" s="469">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="472" t="s">
         <v>630</v>
@@ -37383,7 +37403,7 @@
       <c r="J55" s="483"/>
     </row>
     <row r="56" spans="1:10" s="451" customFormat="1" ht="18" customHeight="1">
-      <c r="A56" s="517" t="s">
+      <c r="A56" s="523" t="s">
         <v>0</v>
       </c>
       <c r="B56" s="588"/>
@@ -37396,15 +37416,15 @@
       <c r="J56" s="483"/>
     </row>
     <row r="57" spans="1:10" s="451" customFormat="1" ht="18" customHeight="1">
-      <c r="A57" s="524" t="s">
+      <c r="A57" s="521" t="s">
         <v>1</v>
       </c>
-      <c r="B57" s="523"/>
-      <c r="C57" s="523"/>
-      <c r="D57" s="523"/>
-      <c r="E57" s="523"/>
-      <c r="F57" s="523"/>
-      <c r="G57" s="523"/>
+      <c r="B57" s="520"/>
+      <c r="C57" s="520"/>
+      <c r="D57" s="520"/>
+      <c r="E57" s="520"/>
+      <c r="F57" s="520"/>
+      <c r="G57" s="520"/>
       <c r="I57" s="466"/>
       <c r="J57" s="483"/>
     </row>
@@ -38194,14 +38214,14 @@
       <c r="E96" s="82"/>
     </row>
     <row r="97" spans="1:10" ht="18" customHeight="1">
-      <c r="A97" s="522" t="s">
+      <c r="A97" s="519" t="s">
         <v>114</v>
       </c>
-      <c r="B97" s="523"/>
-      <c r="C97" s="523"/>
-      <c r="D97" s="523"/>
-      <c r="E97" s="523"/>
-      <c r="F97" s="523"/>
+      <c r="B97" s="520"/>
+      <c r="C97" s="520"/>
+      <c r="D97" s="520"/>
+      <c r="E97" s="520"/>
+      <c r="F97" s="520"/>
     </row>
     <row r="98" spans="1:10" s="451" customFormat="1" ht="18" customHeight="1">
       <c r="A98" s="307">
@@ -38711,7 +38731,7 @@
       <c r="H2" s="152"/>
     </row>
     <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="521" t="s">
+      <c r="A3" s="518" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="516"/>
@@ -38724,12 +38744,12 @@
     </row>
     <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="589"/>
-      <c r="B4" s="523"/>
-      <c r="C4" s="523"/>
-      <c r="D4" s="523"/>
-      <c r="E4" s="523"/>
-      <c r="F4" s="523"/>
-      <c r="G4" s="523"/>
+      <c r="B4" s="520"/>
+      <c r="C4" s="520"/>
+      <c r="D4" s="520"/>
+      <c r="E4" s="520"/>
+      <c r="F4" s="520"/>
+      <c r="G4" s="520"/>
       <c r="H4" s="152"/>
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -39152,7 +39172,7 @@
       </c>
       <c r="G21" s="469">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="152"/>
     </row>
@@ -39792,7 +39812,7 @@
       </c>
       <c r="G47" s="469">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="152"/>
     </row>
@@ -39984,7 +40004,7 @@
       <c r="H55" s="451"/>
     </row>
     <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="517" t="s">
+      <c r="A56" s="523" t="s">
         <v>0</v>
       </c>
       <c r="B56" s="516"/>
@@ -39996,15 +40016,15 @@
       <c r="H56" s="451"/>
     </row>
     <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="524" t="s">
+      <c r="A57" s="521" t="s">
         <v>1</v>
       </c>
-      <c r="B57" s="523"/>
-      <c r="C57" s="523"/>
-      <c r="D57" s="523"/>
-      <c r="E57" s="523"/>
-      <c r="F57" s="523"/>
-      <c r="G57" s="523"/>
+      <c r="B57" s="520"/>
+      <c r="C57" s="520"/>
+      <c r="D57" s="520"/>
+      <c r="E57" s="520"/>
+      <c r="F57" s="520"/>
+      <c r="G57" s="520"/>
       <c r="H57" s="451"/>
     </row>
     <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -40703,14 +40723,14 @@
       <c r="H90" s="152"/>
     </row>
     <row r="91" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="522" t="s">
+      <c r="A91" s="519" t="s">
         <v>114</v>
       </c>
-      <c r="B91" s="523"/>
-      <c r="C91" s="523"/>
-      <c r="D91" s="523"/>
-      <c r="E91" s="523"/>
-      <c r="F91" s="523"/>
+      <c r="B91" s="520"/>
+      <c r="C91" s="520"/>
+      <c r="D91" s="520"/>
+      <c r="E91" s="520"/>
+      <c r="F91" s="520"/>
       <c r="G91" s="152"/>
       <c r="H91" s="152"/>
     </row>
@@ -41306,7 +41326,7 @@
       <c r="H2" s="516"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A3" s="521" t="s">
+      <c r="A3" s="518" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="515"/>
@@ -41318,7 +41338,7 @@
       <c r="H3" s="516"/>
     </row>
     <row r="4" spans="1:8" ht="55.5" hidden="1" customHeight="1">
-      <c r="A4" s="520" t="s">
+      <c r="A4" s="517" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="515"/>
@@ -41377,8 +41397,8 @@
       <c r="D7" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="68">
-        <v>9840850744</v>
+      <c r="E7" s="68" t="s">
+        <v>715</v>
       </c>
       <c r="F7" s="444">
         <v>42387</v>
@@ -41402,8 +41422,8 @@
       <c r="D8" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="68">
-        <v>9908823834</v>
+      <c r="E8" s="68" t="s">
+        <v>715</v>
       </c>
       <c r="F8" s="444">
         <v>39259</v>
@@ -41427,8 +41447,8 @@
       <c r="D9" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="68">
-        <v>9676354404</v>
+      <c r="E9" s="68" t="s">
+        <v>715</v>
       </c>
       <c r="F9" s="445">
         <v>42193</v>
@@ -41452,8 +41472,8 @@
       <c r="D10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="68">
-        <v>8085575111</v>
+      <c r="E10" s="68" t="s">
+        <v>715</v>
       </c>
       <c r="F10" s="95">
         <v>45495</v>
@@ -41477,8 +41497,8 @@
       <c r="D11" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="53">
-        <v>9441536410</v>
+      <c r="E11" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F11" s="446">
         <v>40025</v>
@@ -41502,8 +41522,8 @@
       <c r="D12" s="481" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="68">
-        <v>8297208489</v>
+      <c r="E12" s="68" t="s">
+        <v>715</v>
       </c>
       <c r="F12" s="445">
         <v>40206</v>
@@ -41527,8 +41547,8 @@
       <c r="D13" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="68">
-        <v>9441540580</v>
+      <c r="E13" s="68" t="s">
+        <v>715</v>
       </c>
       <c r="F13" s="445">
         <v>44107</v>
@@ -41552,8 +41572,8 @@
       <c r="D14" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="68">
-        <v>9550367172</v>
+      <c r="E14" s="68" t="s">
+        <v>715</v>
       </c>
       <c r="F14" s="446">
         <v>40032</v>
@@ -41577,8 +41597,8 @@
       <c r="D15" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="53">
-        <v>9848129660</v>
+      <c r="E15" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F15" s="446">
         <v>45084</v>
@@ -41602,8 +41622,8 @@
       <c r="D16" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="53">
-        <v>9994476533</v>
+      <c r="E16" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F16" s="95">
         <v>45103</v>
@@ -41627,8 +41647,8 @@
       <c r="D17" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="53">
-        <v>9848052474</v>
+      <c r="E17" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F17" s="95">
         <v>45103</v>
@@ -41652,8 +41672,8 @@
       <c r="D18" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="53">
-        <v>7981738522</v>
+      <c r="E18" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F18" s="446">
         <v>45139</v>
@@ -41677,8 +41697,8 @@
       <c r="D19" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="56">
-        <v>7006157037</v>
+      <c r="E19" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F19" s="446">
         <v>45289</v>
@@ -41702,8 +41722,8 @@
       <c r="D20" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="53">
-        <v>9032045840</v>
+      <c r="E20" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F20" s="446">
         <v>45632</v>
@@ -41727,8 +41747,8 @@
       <c r="D21" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="53">
-        <v>9614547390</v>
+      <c r="E21" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F21" s="445">
         <v>45014</v>
@@ -41752,15 +41772,15 @@
       <c r="D22" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="53">
-        <v>7729990303</v>
+      <c r="E22" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F22" s="445">
         <v>45047</v>
       </c>
       <c r="G22" s="500">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="69"/>
     </row>
@@ -41777,8 +41797,8 @@
       <c r="D23" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="53">
-        <v>9600605782</v>
+      <c r="E23" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F23" s="95">
         <v>45105</v>
@@ -41802,8 +41822,8 @@
       <c r="D24" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="53">
-        <v>9500312191</v>
+      <c r="E24" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F24" s="95">
         <v>45117</v>
@@ -41827,8 +41847,8 @@
       <c r="D25" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="71">
-        <v>8978116834</v>
+      <c r="E25" s="71" t="s">
+        <v>715</v>
       </c>
       <c r="F25" s="446">
         <v>45121</v>
@@ -41852,8 +41872,8 @@
       <c r="D26" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="56">
-        <v>9440664462</v>
+      <c r="E26" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F26" s="446">
         <v>45600</v>
@@ -41877,8 +41897,8 @@
       <c r="D27" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="56">
-        <v>6300921477</v>
+      <c r="E27" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F27" s="446" t="s">
         <v>40</v>
@@ -41901,8 +41921,8 @@
       <c r="D28" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="56">
-        <v>9492688417</v>
+      <c r="E28" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F28" s="446" t="s">
         <v>43</v>
@@ -41925,8 +41945,8 @@
       <c r="D29" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="56">
-        <v>9494841792</v>
+      <c r="E29" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F29" s="446">
         <v>45838</v>
@@ -41950,8 +41970,8 @@
       <c r="D30" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="68">
-        <v>9493670612</v>
+      <c r="E30" s="68" t="s">
+        <v>715</v>
       </c>
       <c r="F30" s="445">
         <v>42193</v>
@@ -41970,13 +41990,13 @@
         <v>1243</v>
       </c>
       <c r="C31" s="70" t="s">
-        <v>46</v>
+        <v>714</v>
       </c>
       <c r="D31" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="68">
-        <v>8790166779</v>
+      <c r="E31" s="68" t="s">
+        <v>715</v>
       </c>
       <c r="F31" s="445">
         <v>42354</v>
@@ -42000,8 +42020,8 @@
       <c r="D32" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="53">
-        <v>7981960066</v>
+      <c r="E32" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F32" s="95">
         <v>45385</v>
@@ -42025,8 +42045,8 @@
       <c r="D33" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="53">
-        <v>9788682940</v>
+      <c r="E33" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F33" s="446">
         <v>45453</v>
@@ -42050,8 +42070,8 @@
       <c r="D34" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="53">
-        <v>9292709507</v>
+      <c r="E34" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F34" s="445">
         <v>45117</v>
@@ -42075,8 +42095,8 @@
       <c r="D35" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="53">
-        <v>9989895732</v>
+      <c r="E35" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F35" s="446">
         <v>45531</v>
@@ -42100,8 +42120,8 @@
       <c r="D36" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="56">
-        <v>9642674547</v>
+      <c r="E36" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F36" s="446">
         <v>45663</v>
@@ -42125,8 +42145,8 @@
       <c r="D37" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="E37" s="56">
-        <v>8330983764</v>
+      <c r="E37" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F37" s="446">
         <v>45742</v>
@@ -42150,8 +42170,8 @@
       <c r="D38" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="E38" s="56">
-        <v>9885657789</v>
+      <c r="E38" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F38" s="56" t="s">
         <v>55</v>
@@ -42174,8 +42194,8 @@
       <c r="D39" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="E39" s="56">
-        <v>7338323477</v>
+      <c r="E39" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F39" s="56" t="s">
         <v>57</v>
@@ -42198,8 +42218,8 @@
       <c r="D40" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="E40" s="56">
-        <v>9492617314</v>
+      <c r="E40" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F40" s="56" t="s">
         <v>59</v>
@@ -42222,8 +42242,8 @@
       <c r="D41" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="56">
-        <v>9014766760</v>
+      <c r="E41" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F41" s="446">
         <v>45580</v>
@@ -42247,8 +42267,8 @@
       <c r="D42" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="56">
-        <v>8790242128</v>
+      <c r="E42" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F42" s="446">
         <v>45826</v>
@@ -42272,8 +42292,8 @@
       <c r="D43" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="E43" s="56">
-        <v>9491432819</v>
+      <c r="E43" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F43" s="446">
         <v>45845</v>
@@ -42297,8 +42317,8 @@
       <c r="D44" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="56">
-        <v>7995794652</v>
+      <c r="E44" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F44" s="446">
         <v>45582</v>
@@ -42322,8 +42342,8 @@
       <c r="D45" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="56">
-        <v>8125544167</v>
+      <c r="E45" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F45" s="446">
         <v>45600</v>
@@ -42347,8 +42367,8 @@
       <c r="D46" s="307" t="s">
         <v>66</v>
       </c>
-      <c r="E46" s="307">
-        <v>8790500801</v>
+      <c r="E46" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F46" s="446"/>
       <c r="G46" s="500"/>
@@ -42367,15 +42387,15 @@
       <c r="D47" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="E47" s="56">
-        <v>7331142998</v>
+      <c r="E47" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F47" s="446">
         <v>45778</v>
       </c>
       <c r="G47" s="500">
         <f t="shared" ref="G47:G53" ca="1" si="2">DATEDIF(F47,TODAY(),"y")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="69"/>
     </row>
@@ -42392,8 +42412,8 @@
       <c r="D48" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="E48" s="307">
-        <v>7995622962</v>
+      <c r="E48" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F48" s="414">
         <v>44928</v>
@@ -42417,8 +42437,8 @@
       <c r="D49" s="307" t="s">
         <v>71</v>
       </c>
-      <c r="E49" s="307">
-        <v>9381279468</v>
+      <c r="E49" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F49" s="429">
         <v>45964</v>
@@ -42442,8 +42462,8 @@
       <c r="D50" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="E50" s="53">
-        <v>9494678628</v>
+      <c r="E50" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F50" s="95">
         <v>40380</v>
@@ -42467,8 +42487,8 @@
       <c r="D51" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="E51" s="53">
-        <v>9640066261</v>
+      <c r="E51" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F51" s="95">
         <v>44718</v>
@@ -42492,8 +42512,8 @@
       <c r="D52" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="E52" s="53">
-        <v>8074365175</v>
+      <c r="E52" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F52" s="453">
         <v>45993</v>
@@ -42517,8 +42537,8 @@
       <c r="D53" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="E53" s="53">
-        <v>8341185708</v>
+      <c r="E53" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F53" s="453">
         <v>46043</v>
@@ -42534,7 +42554,7 @@
       <c r="G54" s="443"/>
     </row>
     <row r="55" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A55" s="517" t="s">
+      <c r="A55" s="523" t="s">
         <v>0</v>
       </c>
       <c r="B55" s="515"/>
@@ -42545,35 +42565,35 @@
       <c r="G55" s="516"/>
     </row>
     <row r="56" spans="1:8" ht="16.5" hidden="1" customHeight="1">
-      <c r="A56" s="524" t="s">
+      <c r="A56" s="521" t="s">
         <v>1</v>
       </c>
-      <c r="B56" s="523"/>
-      <c r="C56" s="523"/>
-      <c r="D56" s="523"/>
-      <c r="E56" s="523"/>
-      <c r="F56" s="523"/>
-      <c r="G56" s="523"/>
+      <c r="B56" s="520"/>
+      <c r="C56" s="520"/>
+      <c r="D56" s="520"/>
+      <c r="E56" s="520"/>
+      <c r="F56" s="520"/>
+      <c r="G56" s="520"/>
     </row>
     <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="525" t="s">
+      <c r="A57" s="522" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="523"/>
-      <c r="C57" s="523"/>
-      <c r="D57" s="523"/>
-      <c r="E57" s="523"/>
-      <c r="F57" s="523"/>
-      <c r="G57" s="523"/>
-      <c r="H57" s="523"/>
+      <c r="B57" s="520"/>
+      <c r="C57" s="520"/>
+      <c r="D57" s="520"/>
+      <c r="E57" s="520"/>
+      <c r="F57" s="520"/>
+      <c r="G57" s="520"/>
+      <c r="H57" s="520"/>
     </row>
     <row r="58" spans="1:8" ht="9.75" customHeight="1">
-      <c r="A58" s="518"/>
+      <c r="A58" s="524"/>
       <c r="B58" s="515"/>
       <c r="C58" s="516"/>
       <c r="D58" s="516"/>
       <c r="E58" s="516"/>
-      <c r="F58" s="519"/>
+      <c r="F58" s="525"/>
       <c r="G58" s="506"/>
     </row>
     <row r="59" spans="1:8" ht="30" customHeight="1">
@@ -42615,8 +42635,8 @@
       <c r="D60" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E60" s="53">
-        <v>8688928251</v>
+      <c r="E60" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F60" s="95">
         <v>45817</v>
@@ -42637,8 +42657,8 @@
       <c r="D61" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E61" s="53">
-        <v>7569374895</v>
+      <c r="E61" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F61" s="95">
         <v>45834</v>
@@ -42659,8 +42679,8 @@
       <c r="D62" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E62" s="53">
-        <v>9573979580</v>
+      <c r="E62" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F62" s="95">
         <v>45834</v>
@@ -42681,8 +42701,8 @@
       <c r="D63" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E63" s="53">
-        <v>8978224170</v>
+      <c r="E63" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F63" s="95">
         <v>45838</v>
@@ -42703,8 +42723,8 @@
       <c r="D64" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E64" s="53">
-        <v>9398268887</v>
+      <c r="E64" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F64" s="95">
         <v>45838</v>
@@ -42725,8 +42745,8 @@
       <c r="D65" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E65" s="53">
-        <v>6281270604</v>
+      <c r="E65" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F65" s="95">
         <v>45840</v>
@@ -42747,8 +42767,8 @@
       <c r="D66" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E66" s="53">
-        <v>9381847839</v>
+      <c r="E66" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F66" s="95">
         <v>45842</v>
@@ -42769,8 +42789,8 @@
       <c r="D67" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E67" s="53">
-        <v>6300368240</v>
+      <c r="E67" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F67" s="95">
         <v>45843</v>
@@ -42791,8 +42811,8 @@
       <c r="D68" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E68" s="53">
-        <v>9515172678</v>
+      <c r="E68" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F68" s="95" t="s">
         <v>95</v>
@@ -42813,8 +42833,8 @@
       <c r="D69" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E69" s="53">
-        <v>8247017365</v>
+      <c r="E69" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F69" s="95" t="s">
         <v>97</v>
@@ -42835,8 +42855,8 @@
       <c r="D70" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E70" s="53">
-        <v>8125869185</v>
+      <c r="E70" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F70" s="95" t="s">
         <v>97</v>
@@ -42857,8 +42877,8 @@
       <c r="D71" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E71" s="71">
-        <v>9000393290</v>
+      <c r="E71" s="71" t="s">
+        <v>715</v>
       </c>
       <c r="F71" s="445">
         <v>45847</v>
@@ -42879,8 +42899,8 @@
       <c r="D72" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E72" s="53">
-        <v>7995627385</v>
+      <c r="E72" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F72" s="95" t="s">
         <v>101</v>
@@ -42901,8 +42921,8 @@
       <c r="D73" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E73" s="53">
-        <v>7013229574</v>
+      <c r="E73" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F73" s="95" t="s">
         <v>103</v>
@@ -42923,8 +42943,8 @@
       <c r="D74" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E74" s="53">
-        <v>9652560279</v>
+      <c r="E74" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F74" s="95">
         <v>45864</v>
@@ -42945,8 +42965,8 @@
       <c r="D75" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E75" s="53">
-        <v>8125941185</v>
+      <c r="E75" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F75" s="95">
         <v>45867</v>
@@ -42967,8 +42987,8 @@
       <c r="D76" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E76" s="53">
-        <v>8309517227</v>
+      <c r="E76" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F76" s="95">
         <v>45869</v>
@@ -42989,8 +43009,8 @@
       <c r="D77" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E77" s="53">
-        <v>9030272655</v>
+      <c r="E77" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F77" s="446">
         <v>45891</v>
@@ -43011,8 +43031,8 @@
       <c r="D78" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E78" s="53">
-        <v>8019998514</v>
+      <c r="E78" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F78" s="445">
         <v>45891</v>
@@ -43033,8 +43053,8 @@
       <c r="D79" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E79" s="53">
-        <v>9848498113</v>
+      <c r="E79" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F79" s="446">
         <v>45894</v>
@@ -43055,8 +43075,8 @@
       <c r="D80" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E80" s="76">
-        <v>6303002425</v>
+      <c r="E80" s="594" t="s">
+        <v>715</v>
       </c>
       <c r="F80" s="95">
         <v>45901</v>
@@ -43077,8 +43097,8 @@
       <c r="D81" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E81" s="56">
-        <v>9701582164</v>
+      <c r="E81" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F81" s="446">
         <v>46022</v>
@@ -43099,8 +43119,8 @@
       <c r="D82" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E82" s="56">
-        <v>9705642369</v>
+      <c r="E82" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F82" s="56"/>
       <c r="G82" s="472"/>
@@ -43117,8 +43137,8 @@
       <c r="D83" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E83" s="56">
-        <v>8978152877</v>
+      <c r="E83" s="56" t="s">
+        <v>715</v>
       </c>
       <c r="F83" s="56"/>
       <c r="G83" s="472"/>
@@ -43134,14 +43154,14 @@
       <c r="G84" s="152"/>
     </row>
     <row r="85" spans="1:8" ht="15" customHeight="1">
-      <c r="A85" s="522" t="s">
+      <c r="A85" s="519" t="s">
         <v>114</v>
       </c>
-      <c r="B85" s="523"/>
-      <c r="C85" s="523"/>
-      <c r="D85" s="523"/>
-      <c r="E85" s="523"/>
-      <c r="F85" s="523"/>
+      <c r="B85" s="520"/>
+      <c r="C85" s="520"/>
+      <c r="D85" s="520"/>
+      <c r="E85" s="520"/>
+      <c r="F85" s="520"/>
       <c r="G85" s="152"/>
     </row>
     <row r="86" spans="1:8" ht="20.100000000000001" customHeight="1">
@@ -43157,8 +43177,8 @@
       <c r="D86" s="461" t="s">
         <v>116</v>
       </c>
-      <c r="E86" s="307">
-        <v>6300035358</v>
+      <c r="E86" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F86" s="462">
         <v>45253</v>
@@ -43178,8 +43198,8 @@
       <c r="D87" s="461" t="s">
         <v>116</v>
       </c>
-      <c r="E87" s="307">
-        <v>8247346900</v>
+      <c r="E87" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F87" s="462">
         <v>45282</v>
@@ -43199,8 +43219,8 @@
       <c r="D88" s="461" t="s">
         <v>119</v>
       </c>
-      <c r="E88" s="307">
-        <v>7981683088</v>
+      <c r="E88" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F88" s="462">
         <v>45513</v>
@@ -43220,8 +43240,8 @@
       <c r="D89" s="461" t="s">
         <v>119</v>
       </c>
-      <c r="E89" s="307">
-        <v>7672052900</v>
+      <c r="E89" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F89" s="462">
         <v>45597</v>
@@ -43241,8 +43261,8 @@
       <c r="D90" s="461" t="s">
         <v>119</v>
       </c>
-      <c r="E90" s="307">
-        <v>9948686959</v>
+      <c r="E90" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F90" s="462">
         <v>45600</v>
@@ -43262,8 +43282,8 @@
       <c r="D91" s="461" t="s">
         <v>119</v>
       </c>
-      <c r="E91" s="307">
-        <v>7799595004</v>
+      <c r="E91" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F91" s="462">
         <v>45610</v>
@@ -43283,8 +43303,8 @@
       <c r="D92" s="461" t="s">
         <v>119</v>
       </c>
-      <c r="E92" s="307">
-        <v>6302946907</v>
+      <c r="E92" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F92" s="403" t="s">
         <v>124</v>
@@ -43304,8 +43324,8 @@
       <c r="D93" s="461" t="s">
         <v>119</v>
       </c>
-      <c r="E93" s="307">
-        <v>9182194446</v>
+      <c r="E93" s="307" t="s">
+        <v>715</v>
       </c>
       <c r="F93" s="462">
         <v>45726</v>
@@ -43325,8 +43345,8 @@
       <c r="D94" s="461" t="s">
         <v>119</v>
       </c>
-      <c r="E94" s="403">
-        <v>8341287184</v>
+      <c r="E94" s="403" t="s">
+        <v>715</v>
       </c>
       <c r="F94" s="403" t="s">
         <v>127</v>
@@ -43346,8 +43366,8 @@
       <c r="D95" s="461" t="s">
         <v>119</v>
       </c>
-      <c r="E95" s="403">
-        <v>9569464941</v>
+      <c r="E95" s="403" t="s">
+        <v>715</v>
       </c>
       <c r="F95" s="403" t="s">
         <v>129</v>
@@ -43367,8 +43387,8 @@
       <c r="D96" s="461" t="s">
         <v>119</v>
       </c>
-      <c r="E96" s="403">
-        <v>9492426713</v>
+      <c r="E96" s="403" t="s">
+        <v>715</v>
       </c>
       <c r="F96" s="403" t="s">
         <v>131</v>
@@ -43388,8 +43408,8 @@
       <c r="D97" s="461" t="s">
         <v>119</v>
       </c>
-      <c r="E97" s="403">
-        <v>7013885810</v>
+      <c r="E97" s="403" t="s">
+        <v>715</v>
       </c>
       <c r="F97" s="462">
         <v>45853</v>
@@ -43410,7 +43430,7 @@
         <v>119</v>
       </c>
       <c r="E98" s="403" t="s">
-        <v>134</v>
+        <v>715</v>
       </c>
       <c r="F98" s="507">
         <v>45918</v>
@@ -43448,8 +43468,8 @@
       <c r="D101" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="E101" s="53">
-        <v>9502200265</v>
+      <c r="E101" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F101" s="509">
         <v>40299</v>
@@ -43470,7 +43490,7 @@
         <v>136</v>
       </c>
       <c r="E102" s="53" t="s">
-        <v>138</v>
+        <v>715</v>
       </c>
       <c r="F102" s="429">
         <v>45887</v>
@@ -43490,8 +43510,8 @@
       <c r="D103" s="56" t="s">
         <v>140</v>
       </c>
-      <c r="E103" s="53">
-        <v>9573912337</v>
+      <c r="E103" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F103" s="429">
         <v>45198</v>
@@ -43511,8 +43531,8 @@
       <c r="D104" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="E104" s="53">
-        <v>7416390127</v>
+      <c r="E104" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F104" s="429">
         <v>45293</v>
@@ -43532,8 +43552,8 @@
       <c r="D105" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="E105" s="53">
-        <v>8142888477</v>
+      <c r="E105" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="F105" s="429">
         <v>45700</v>
@@ -43617,15 +43637,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A56:G56"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A55:G55"/>
     <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="B21:B22">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
@@ -48141,31 +48161,31 @@
       <c r="A1" s="514" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="536"/>
-      <c r="C1" s="536"/>
-      <c r="D1" s="536"/>
-      <c r="E1" s="537"/>
-      <c r="F1" s="537"/>
+      <c r="B1" s="534"/>
+      <c r="C1" s="534"/>
+      <c r="D1" s="534"/>
+      <c r="E1" s="535"/>
+      <c r="F1" s="535"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1">
       <c r="A2" s="514" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="536"/>
-      <c r="C2" s="536"/>
-      <c r="D2" s="536"/>
-      <c r="E2" s="537"/>
-      <c r="F2" s="537"/>
+      <c r="B2" s="534"/>
+      <c r="C2" s="534"/>
+      <c r="D2" s="534"/>
+      <c r="E2" s="535"/>
+      <c r="F2" s="535"/>
     </row>
     <row r="3" spans="1:6" ht="22.5" customHeight="1">
-      <c r="A3" s="522" t="s">
+      <c r="A3" s="519" t="s">
         <v>372</v>
       </c>
-      <c r="B3" s="523"/>
-      <c r="C3" s="523"/>
-      <c r="D3" s="523"/>
-      <c r="E3" s="523"/>
-      <c r="F3" s="523"/>
+      <c r="B3" s="520"/>
+      <c r="C3" s="520"/>
+      <c r="D3" s="520"/>
+      <c r="E3" s="520"/>
+      <c r="F3" s="520"/>
     </row>
     <row r="4" spans="1:6" ht="36" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -48909,39 +48929,39 @@
       <c r="A45" s="514" t="s">
         <v>0</v>
       </c>
-      <c r="B45" s="536"/>
-      <c r="C45" s="536"/>
-      <c r="D45" s="536"/>
-      <c r="E45" s="537"/>
-      <c r="F45" s="537"/>
+      <c r="B45" s="534"/>
+      <c r="C45" s="534"/>
+      <c r="D45" s="534"/>
+      <c r="E45" s="535"/>
+      <c r="F45" s="535"/>
     </row>
     <row r="46" spans="1:6" ht="19.5" customHeight="1">
       <c r="A46" s="514" t="s">
         <v>1</v>
       </c>
-      <c r="B46" s="536"/>
-      <c r="C46" s="536"/>
-      <c r="D46" s="536"/>
-      <c r="E46" s="537"/>
-      <c r="F46" s="537"/>
+      <c r="B46" s="534"/>
+      <c r="C46" s="534"/>
+      <c r="D46" s="534"/>
+      <c r="E46" s="535"/>
+      <c r="F46" s="535"/>
     </row>
     <row r="47" spans="1:6" ht="21" customHeight="1">
       <c r="A47" s="538" t="s">
         <v>379</v>
       </c>
-      <c r="B47" s="536"/>
-      <c r="C47" s="536"/>
-      <c r="D47" s="536"/>
-      <c r="E47" s="537"/>
-      <c r="F47" s="537"/>
+      <c r="B47" s="534"/>
+      <c r="C47" s="534"/>
+      <c r="D47" s="534"/>
+      <c r="E47" s="535"/>
+      <c r="F47" s="535"/>
     </row>
     <row r="48" spans="1:6" ht="21" customHeight="1">
-      <c r="A48" s="534"/>
-      <c r="B48" s="523"/>
-      <c r="C48" s="523"/>
-      <c r="D48" s="523"/>
-      <c r="E48" s="523"/>
-      <c r="F48" s="535"/>
+      <c r="A48" s="536"/>
+      <c r="B48" s="520"/>
+      <c r="C48" s="520"/>
+      <c r="D48" s="520"/>
+      <c r="E48" s="520"/>
+      <c r="F48" s="537"/>
     </row>
     <row r="49" spans="1:6" ht="21" customHeight="1">
       <c r="A49" s="116" t="s">
@@ -49905,12 +49925,12 @@
       <c r="G3" s="539"/>
     </row>
     <row r="4" spans="2:7" ht="15.6">
-      <c r="B4" s="522"/>
-      <c r="C4" s="523"/>
-      <c r="D4" s="523"/>
-      <c r="E4" s="523"/>
-      <c r="F4" s="523"/>
-      <c r="G4" s="523"/>
+      <c r="B4" s="519"/>
+      <c r="C4" s="520"/>
+      <c r="D4" s="520"/>
+      <c r="E4" s="520"/>
+      <c r="F4" s="520"/>
+      <c r="G4" s="520"/>
     </row>
     <row r="5" spans="2:7" ht="24.9" customHeight="1">
       <c r="B5" s="3" t="s">
@@ -51136,11 +51156,11 @@
       <c r="E2" s="515"/>
     </row>
     <row r="3" spans="1:5" ht="3.75" customHeight="1">
-      <c r="A3" s="522"/>
-      <c r="B3" s="523"/>
-      <c r="C3" s="523"/>
-      <c r="D3" s="523"/>
-      <c r="E3" s="523"/>
+      <c r="A3" s="519"/>
+      <c r="B3" s="520"/>
+      <c r="C3" s="520"/>
+      <c r="D3" s="520"/>
+      <c r="E3" s="520"/>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -52195,13 +52215,13 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="522" t="s">
+      <c r="A62" s="519" t="s">
         <v>114</v>
       </c>
-      <c r="B62" s="523"/>
-      <c r="C62" s="523"/>
-      <c r="D62" s="523"/>
-      <c r="E62" s="523"/>
+      <c r="B62" s="520"/>
+      <c r="C62" s="520"/>
+      <c r="D62" s="520"/>
+      <c r="E62" s="520"/>
     </row>
     <row r="63" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A63" s="53">
@@ -52355,10 +52375,10 @@
       <c r="A73" s="542" t="s">
         <v>411</v>
       </c>
-      <c r="B73" s="523"/>
-      <c r="C73" s="523"/>
-      <c r="D73" s="523"/>
-      <c r="E73" s="523"/>
+      <c r="B73" s="520"/>
+      <c r="C73" s="520"/>
+      <c r="D73" s="520"/>
+      <c r="E73" s="520"/>
     </row>
     <row r="74" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A74" s="53">
@@ -52509,11 +52529,11 @@
       <c r="E2" s="516"/>
     </row>
     <row r="3" spans="1:5" ht="8.25" customHeight="1">
-      <c r="A3" s="522"/>
-      <c r="B3" s="523"/>
-      <c r="C3" s="523"/>
-      <c r="D3" s="523"/>
-      <c r="E3" s="523"/>
+      <c r="A3" s="519"/>
+      <c r="B3" s="520"/>
+      <c r="C3" s="520"/>
+      <c r="D3" s="520"/>
+      <c r="E3" s="520"/>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -53333,13 +53353,13 @@
       <c r="E53" s="81"/>
     </row>
     <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="522" t="s">
+      <c r="A54" s="519" t="s">
         <v>114</v>
       </c>
-      <c r="B54" s="523"/>
-      <c r="C54" s="523"/>
-      <c r="D54" s="523"/>
-      <c r="E54" s="523"/>
+      <c r="B54" s="520"/>
+      <c r="C54" s="520"/>
+      <c r="D54" s="520"/>
+      <c r="E54" s="520"/>
     </row>
     <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A55" s="53">
@@ -53495,10 +53515,10 @@
       <c r="A65" s="542" t="s">
         <v>411</v>
       </c>
-      <c r="B65" s="523"/>
-      <c r="C65" s="523"/>
-      <c r="D65" s="523"/>
-      <c r="E65" s="523"/>
+      <c r="B65" s="520"/>
+      <c r="C65" s="520"/>
+      <c r="D65" s="520"/>
+      <c r="E65" s="520"/>
     </row>
     <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A66" s="53">
@@ -53626,10 +53646,10 @@
     </row>
     <row r="3" spans="1:6" ht="2.25" customHeight="1">
       <c r="A3" s="546"/>
-      <c r="B3" s="523"/>
-      <c r="C3" s="523"/>
-      <c r="D3" s="523"/>
-      <c r="E3" s="523"/>
+      <c r="B3" s="520"/>
+      <c r="C3" s="520"/>
+      <c r="D3" s="520"/>
+      <c r="E3" s="520"/>
       <c r="F3" s="313"/>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1">
@@ -56242,10 +56262,10 @@
       <c r="A68" s="542" t="s">
         <v>411</v>
       </c>
-      <c r="B68" s="523"/>
-      <c r="C68" s="523"/>
-      <c r="D68" s="523"/>
-      <c r="E68" s="523"/>
+      <c r="B68" s="520"/>
+      <c r="C68" s="520"/>
+      <c r="D68" s="520"/>
+      <c r="E68" s="520"/>
     </row>
     <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A69" s="53">
